--- a/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/data/D4_pair_profile_summary.xlsx
+++ b/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/data/D4_pair_profile_summary.xlsx
@@ -537,43 +537,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3.394775810721377</v>
+        <v>3.50482412477186</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4</v>
+        <v>3.525</v>
       </c>
       <c r="G2" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="H2" t="n">
-        <v>3.395028550148957</v>
+        <v>3.50482412477186</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9874203561509557</v>
+        <v>0.9846430321842836</v>
       </c>
       <c r="J2" t="n">
         <v>0.2465283450416599</v>
       </c>
       <c r="K2" t="n">
-        <v>0.002940695964711648</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>3.793007678483908</v>
+        <v>4.094242575078812</v>
       </c>
       <c r="M2" t="n">
-        <v>4.056853455317759</v>
+        <v>4.097892815662851</v>
       </c>
       <c r="N2" t="n">
-        <v>4.103414474759027</v>
+        <v>4.141554782032157</v>
       </c>
       <c r="O2" t="n">
         <v>2.771932690736808</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2908669755129054</v>
+        <v>0.2254853160776506</v>
       </c>
       <c r="Q2" t="n">
-        <v>116</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3">
@@ -598,43 +598,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3.421027708850289</v>
+        <v>3.503225070516011</v>
       </c>
       <c r="F3" t="n">
-        <v>3.4</v>
+        <v>3.4625</v>
       </c>
       <c r="G3" t="n">
-        <v>2.125</v>
+        <v>2.3875</v>
       </c>
       <c r="H3" t="n">
-        <v>3.420809200728115</v>
+        <v>3.503225070516011</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9875837281489953</v>
+        <v>0.9846430321842836</v>
       </c>
       <c r="J3" t="n">
         <v>0.006534879921581441</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00326743996079072</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>4.20094755758863</v>
+        <v>4.405176704828273</v>
       </c>
       <c r="M3" t="n">
-        <v>4.039209279529489</v>
+        <v>4.086112493777999</v>
       </c>
       <c r="N3" t="n">
-        <v>3.931710504819474</v>
+        <v>4.003816160610586</v>
       </c>
       <c r="O3" t="n">
         <v>2.623917660512988</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2489660876757651</v>
+        <v>0.1939605110336818</v>
       </c>
       <c r="Q3" t="n">
-        <v>113</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4">
@@ -659,43 +659,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3.258610421836228</v>
+        <v>3.378853492616559</v>
       </c>
       <c r="F4" t="n">
-        <v>3.25</v>
+        <v>3.3875</v>
       </c>
       <c r="G4" t="n">
-        <v>2.05</v>
+        <v>2.4125</v>
       </c>
       <c r="H4" t="n">
-        <v>3.259457223233494</v>
+        <v>3.378853492616559</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9875837281489953</v>
+        <v>0.9846430321842836</v>
       </c>
       <c r="J4" t="n">
         <v>0.000326743996079072</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00326743996079072</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>3.987910472145074</v>
+        <v>4.264476522316244</v>
       </c>
       <c r="M4" t="n">
-        <v>3.851168109785983</v>
+        <v>3.915380786460926</v>
       </c>
       <c r="N4" t="n">
-        <v>3.586178728965855</v>
+        <v>3.702007632321221</v>
       </c>
       <c r="O4" t="n">
-        <v>2.76409083483091</v>
+        <v>2.756085606926973</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3655913978494624</v>
+        <v>0.2475526796084287</v>
       </c>
       <c r="Q4" t="n">
-        <v>165</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5">
@@ -720,43 +720,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3.022140198511166</v>
+        <v>3.204583540733366</v>
       </c>
       <c r="F5" t="n">
-        <v>3.1375</v>
+        <v>3.3</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5625</v>
+        <v>1.675</v>
       </c>
       <c r="H5" t="n">
-        <v>3.023862320039715</v>
+        <v>3.204583540733366</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9875837281489953</v>
+        <v>0.9846430321842836</v>
       </c>
       <c r="J5" t="n">
         <v>0.657408920111093</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004247671949027937</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>3.027936611664761</v>
+        <v>3.538078646092583</v>
       </c>
       <c r="M5" t="n">
-        <v>4.20764580950825</v>
+        <v>4.240584038493446</v>
       </c>
       <c r="N5" t="n">
-        <v>4.020421499754942</v>
+        <v>4.08089444261756</v>
       </c>
       <c r="O5" t="n">
         <v>2.42607417088711</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4574028122415219</v>
+        <v>0.3641944582711133</v>
       </c>
       <c r="Q5" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6">
@@ -781,43 +781,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3.481237631926121</v>
+        <v>3.876366766218682</v>
       </c>
       <c r="F6" t="n">
-        <v>3.4875</v>
+        <v>3.8</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1625</v>
+        <v>2.7625</v>
       </c>
       <c r="H6" t="n">
-        <v>3.480905641702408</v>
+        <v>3.876366766218682</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9906877961117464</v>
+        <v>0.9846430321842836</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2238196373141643</v>
+        <v>0.224309753308283</v>
       </c>
       <c r="K6" t="n">
-        <v>0.000980231988237216</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>3.924358764907695</v>
+        <v>4.491289198606272</v>
       </c>
       <c r="M6" t="n">
-        <v>4.10913249469041</v>
+        <v>4.376306620209059</v>
       </c>
       <c r="N6" t="n">
-        <v>3.955726188531286</v>
+        <v>4.606895414054767</v>
       </c>
       <c r="O6" t="n">
-        <v>3.139356314327724</v>
+        <v>3.170887109949355</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2521437994722955</v>
+        <v>0.09407665505226481</v>
       </c>
       <c r="Q6" t="n">
-        <v>107</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
@@ -842,43 +842,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2.971229798812665</v>
+        <v>3.514671478347436</v>
       </c>
       <c r="F7" t="n">
-        <v>2.875</v>
+        <v>3.5375</v>
       </c>
       <c r="G7" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>2.971348152424942</v>
+        <v>3.514671478347436</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9906877961117464</v>
+        <v>0.9846430321842836</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02728312367260251</v>
+        <v>0.02744649567064205</v>
       </c>
       <c r="K7" t="n">
-        <v>0.006044763927462833</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3.070249959157</v>
+        <v>3.774514683922349</v>
       </c>
       <c r="M7" t="n">
-        <v>3.886293089364483</v>
+        <v>4.1750456280073</v>
       </c>
       <c r="N7" t="n">
-        <v>2.714262375428851</v>
+        <v>3.694310830983579</v>
       </c>
       <c r="O7" t="n">
         <v>3.529488645646136</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5371042216358839</v>
+        <v>0.2769205243072839</v>
       </c>
       <c r="Q7" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8">
@@ -903,43 +903,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2.588710009894459</v>
+        <v>3.098218433714949</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5</v>
+        <v>3.0875</v>
       </c>
       <c r="G8" t="n">
-        <v>1.45</v>
+        <v>1.8625</v>
       </c>
       <c r="H8" t="n">
-        <v>2.588615555922138</v>
+        <v>3.098218433714949</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9906877961117464</v>
+        <v>0.9846430321842836</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.00163371998039536</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2.923868648913576</v>
+        <v>3.566119130579061</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2888416925339</v>
+        <v>3.67479674796748</v>
       </c>
       <c r="N8" t="n">
-        <v>2.558568861297174</v>
+        <v>3.532769205243073</v>
       </c>
       <c r="O8" t="n">
         <v>2.840222185917334</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7074538258575198</v>
+        <v>0.4519661523145844</v>
       </c>
       <c r="Q8" t="n">
-        <v>155</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
